--- a/main/ig/CodeSystem-competence-code-system.xlsx
+++ b/main/ig/CodeSystem-competence-code-system.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/[code]/CodeSystem/competence-code-system</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/fr-patient-summary/CodeSystem/competence-code-system</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T10:54:04+00:00</t>
+    <t>2026-09-25T07:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
